--- a/IV_2.5K_T2.xlsx
+++ b/IV_2.5K_T2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3149,7 +3149,7 @@
         <v>26.5625</v>
       </c>
       <c r="AT22">
-        <v>4.6469999999999997E-2</v>
+        <v>4.648E-2</v>
       </c>
     </row>
     <row r="23" spans="1:46" x14ac:dyDescent="0.25">
@@ -3289,7 +3289,7 @@
         <v>28.125</v>
       </c>
       <c r="AT23">
-        <v>4.9230000000000003E-2</v>
+        <v>4.9209999999999997E-2</v>
       </c>
     </row>
     <row r="24" spans="1:46" x14ac:dyDescent="0.25">
@@ -3429,7 +3429,7 @@
         <v>29.6875</v>
       </c>
       <c r="AT24">
-        <v>5.1959999999999999E-2</v>
+        <v>5.1920000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:46" x14ac:dyDescent="0.25">
@@ -3569,7 +3569,7 @@
         <v>31.25</v>
       </c>
       <c r="AT25">
-        <v>5.4699999999999999E-2</v>
+        <v>5.4710000000000002E-2</v>
       </c>
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
         <v>32.8125</v>
       </c>
       <c r="AT26">
-        <v>5.7450000000000001E-2</v>
+        <v>5.7419999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:46" x14ac:dyDescent="0.25">
@@ -3849,7 +3849,7 @@
         <v>34.375</v>
       </c>
       <c r="AT27">
-        <v>6.019E-2</v>
+        <v>6.021E-2</v>
       </c>
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.25">
@@ -3989,7 +3989,7 @@
         <v>35.9375</v>
       </c>
       <c r="AT28">
-        <v>6.2920000000000004E-2</v>
+        <v>6.2899999999999998E-2</v>
       </c>
     </row>
     <row r="29" spans="1:46" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>37.5</v>
       </c>
       <c r="AL29" s="1">
-        <v>6.5659999999999996E-2</v>
+        <v>6.5710000000000005E-2</v>
       </c>
       <c r="AM29">
         <v>37.5</v>
@@ -4129,7 +4129,7 @@
         <v>37.5</v>
       </c>
       <c r="AT29">
-        <v>6.5680000000000002E-2</v>
+        <v>6.5710000000000005E-2</v>
       </c>
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
@@ -4245,7 +4245,7 @@
         <v>39.0625</v>
       </c>
       <c r="AL30" s="1">
-        <v>6.8409999999999999E-2</v>
+        <v>6.8419999999999995E-2</v>
       </c>
       <c r="AM30">
         <v>39.0625</v>
@@ -4269,7 +4269,7 @@
         <v>39.0625</v>
       </c>
       <c r="AT30">
-        <v>6.8409999999999999E-2</v>
+        <v>6.8430000000000005E-2</v>
       </c>
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
@@ -4385,7 +4385,7 @@
         <v>40.625</v>
       </c>
       <c r="AL31" s="1">
-        <v>7.1129999999999999E-2</v>
+        <v>7.1139999999999995E-2</v>
       </c>
       <c r="AM31">
         <v>40.625</v>
@@ -4409,7 +4409,7 @@
         <v>40.625</v>
       </c>
       <c r="AT31">
-        <v>7.1169999999999997E-2</v>
+        <v>7.1179999999999993E-2</v>
       </c>
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>42.1875</v>
       </c>
       <c r="AL32" s="1">
-        <v>7.3880000000000001E-2</v>
+        <v>7.3819999999999997E-2</v>
       </c>
       <c r="AM32">
         <v>42.1875</v>
@@ -4549,7 +4549,7 @@
         <v>42.1875</v>
       </c>
       <c r="AT32">
-        <v>7.3709999999999998E-2</v>
+        <v>7.3749999999999996E-2</v>
       </c>
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
@@ -4665,7 +4665,7 @@
         <v>43.75</v>
       </c>
       <c r="AL33" s="1">
-        <v>7.6619999999999994E-2</v>
+        <v>7.6660000000000006E-2</v>
       </c>
       <c r="AM33">
         <v>43.75</v>
@@ -4689,7 +4689,7 @@
         <v>43.75</v>
       </c>
       <c r="AT33">
-        <v>7.6429999999999998E-2</v>
+        <v>7.6420000000000002E-2</v>
       </c>
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.25">
@@ -4805,7 +4805,7 @@
         <v>45.3125</v>
       </c>
       <c r="AL34" s="1">
-        <v>7.9350000000000004E-2</v>
+        <v>7.9380000000000006E-2</v>
       </c>
       <c r="AM34">
         <v>45.3125</v>
@@ -4969,7 +4969,7 @@
         <v>46.875</v>
       </c>
       <c r="AT35">
-        <v>8.1890000000000004E-2</v>
+        <v>8.1909999999999997E-2</v>
       </c>
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
@@ -5085,7 +5085,7 @@
         <v>48.4375</v>
       </c>
       <c r="AL36" s="1">
-        <v>8.4820000000000007E-2</v>
+        <v>8.4849999999999995E-2</v>
       </c>
       <c r="AM36">
         <v>48.4375</v>
@@ -5109,7 +5109,7 @@
         <v>48.4375</v>
       </c>
       <c r="AT36">
-        <v>8.4629999999999997E-2</v>
+        <v>8.4650000000000003E-2</v>
       </c>
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
@@ -5213,7 +5213,7 @@
         <v>50</v>
       </c>
       <c r="AH37">
-        <v>8.7690000000000004E-2</v>
+        <v>8.7709999999999996E-2</v>
       </c>
       <c r="AI37">
         <v>50</v>
@@ -5225,7 +5225,7 @@
         <v>50</v>
       </c>
       <c r="AL37" s="1">
-        <v>8.7660000000000002E-2</v>
+        <v>8.7709999999999996E-2</v>
       </c>
       <c r="AM37">
         <v>50</v>
@@ -5249,7 +5249,7 @@
         <v>50</v>
       </c>
       <c r="AT37">
-        <v>8.745E-2</v>
+        <v>8.7440000000000004E-2</v>
       </c>
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>51.5625</v>
       </c>
       <c r="AH38">
-        <v>9.042E-2</v>
+        <v>9.0429999999999996E-2</v>
       </c>
       <c r="AI38">
         <v>51.5625</v>
@@ -5365,7 +5365,7 @@
         <v>51.5625</v>
       </c>
       <c r="AL38" s="1">
-        <v>9.0399999999999994E-2</v>
+        <v>9.0380000000000002E-2</v>
       </c>
       <c r="AM38">
         <v>51.5625</v>
@@ -5633,7 +5633,7 @@
         <v>54.6875</v>
       </c>
       <c r="AH40">
-        <v>9.5909999999999995E-2</v>
+        <v>9.5899999999999999E-2</v>
       </c>
       <c r="AI40">
         <v>54.6875</v>
@@ -5645,7 +5645,7 @@
         <v>54.6875</v>
       </c>
       <c r="AL40" s="1">
-        <v>9.5869999999999997E-2</v>
+        <v>9.5909999999999995E-2</v>
       </c>
       <c r="AM40">
         <v>54.6875</v>
@@ -5773,7 +5773,7 @@
         <v>56.25</v>
       </c>
       <c r="AH41">
-        <v>9.8629999999999995E-2</v>
+        <v>9.8589999999999997E-2</v>
       </c>
       <c r="AI41">
         <v>56.25</v>
@@ -5785,7 +5785,7 @@
         <v>56.25</v>
       </c>
       <c r="AL41" s="1">
-        <v>9.8629999999999995E-2</v>
+        <v>9.8680000000000004E-2</v>
       </c>
       <c r="AM41">
         <v>56.25</v>
@@ -5913,7 +5913,7 @@
         <v>57.8125</v>
       </c>
       <c r="AH42">
-        <v>0.10138</v>
+        <v>0.10141</v>
       </c>
       <c r="AI42">
         <v>57.8125</v>
@@ -6193,7 +6193,7 @@
         <v>60.9375</v>
       </c>
       <c r="AH44">
-        <v>0.10687000000000001</v>
+        <v>0.10691000000000001</v>
       </c>
       <c r="AI44">
         <v>60.9375</v>
@@ -6333,7 +6333,7 @@
         <v>62.5</v>
       </c>
       <c r="AH45">
-        <v>0.10963000000000001</v>
+        <v>0.10968</v>
       </c>
       <c r="AI45">
         <v>62.5</v>
@@ -6619,7 +6619,7 @@
         <v>65.625</v>
       </c>
       <c r="AJ47">
-        <v>0.11479</v>
+        <v>0.11483</v>
       </c>
       <c r="AK47">
         <v>65.625</v>
@@ -6759,7 +6759,7 @@
         <v>67.1875</v>
       </c>
       <c r="AJ48">
-        <v>0.11753</v>
+        <v>0.11752</v>
       </c>
       <c r="AK48">
         <v>67.1875</v>
@@ -6899,7 +6899,7 @@
         <v>68.75</v>
       </c>
       <c r="AJ49">
-        <v>0.12026000000000001</v>
+        <v>0.12031</v>
       </c>
       <c r="AK49">
         <v>68.75</v>
@@ -7039,7 +7039,7 @@
         <v>70.3125</v>
       </c>
       <c r="AJ50">
-        <v>0.123</v>
+        <v>0.1226</v>
       </c>
       <c r="AK50">
         <v>70.3125</v>
@@ -7179,7 +7179,7 @@
         <v>71.875</v>
       </c>
       <c r="AJ51">
-        <v>0.12573999999999999</v>
+        <v>0.12578</v>
       </c>
       <c r="AK51">
         <v>71.875</v>
@@ -9103,7 +9103,7 @@
         <v>93.75</v>
       </c>
       <c r="X65">
-        <v>0.16553000000000001</v>
+        <v>0.16556000000000001</v>
       </c>
       <c r="Y65">
         <v>93.75</v>
@@ -9243,7 +9243,7 @@
         <v>95.3125</v>
       </c>
       <c r="X66">
-        <v>0.16830000000000001</v>
+        <v>0.16819999999999999</v>
       </c>
       <c r="Y66">
         <v>95.3125</v>
@@ -9383,7 +9383,7 @@
         <v>96.875</v>
       </c>
       <c r="X67">
-        <v>0.17107</v>
+        <v>0.17108000000000001</v>
       </c>
       <c r="Y67">
         <v>96.875</v>
@@ -9511,7 +9511,7 @@
         <v>98.4375</v>
       </c>
       <c r="T68">
-        <v>0.17385999999999999</v>
+        <v>0.17391000000000001</v>
       </c>
       <c r="U68">
         <v>98.4375</v>
@@ -9523,7 +9523,7 @@
         <v>98.4375</v>
       </c>
       <c r="X68">
-        <v>0.17383999999999999</v>
+        <v>0.17385</v>
       </c>
       <c r="Y68">
         <v>98.4375</v>
@@ -9651,7 +9651,7 @@
         <v>100</v>
       </c>
       <c r="T69">
-        <v>0.17626</v>
+        <v>0.17624999999999999</v>
       </c>
       <c r="U69">
         <v>100</v>
@@ -9791,7 +9791,7 @@
         <v>98.4375</v>
       </c>
       <c r="T70">
-        <v>0.17349000000000001</v>
+        <v>0.17351</v>
       </c>
       <c r="U70">
         <v>98.4375</v>
@@ -9803,7 +9803,7 @@
         <v>98.4375</v>
       </c>
       <c r="X70">
-        <v>0.17349000000000001</v>
+        <v>0.17351</v>
       </c>
       <c r="Y70">
         <v>98.4375</v>
@@ -9931,7 +9931,7 @@
         <v>96.875</v>
       </c>
       <c r="T71">
-        <v>0.17072000000000001</v>
+        <v>0.17072999999999999</v>
       </c>
       <c r="U71">
         <v>96.875</v>
@@ -9943,7 +9943,7 @@
         <v>96.875</v>
       </c>
       <c r="X71">
-        <v>0.17072000000000001</v>
+        <v>0.17075000000000001</v>
       </c>
       <c r="Y71">
         <v>96.875</v>
@@ -10351,7 +10351,7 @@
         <v>92.1875</v>
       </c>
       <c r="T74">
-        <v>0.16242999999999999</v>
+        <v>0.16239999999999999</v>
       </c>
       <c r="U74">
         <v>92.1875</v>
@@ -10491,7 +10491,7 @@
         <v>90.625</v>
       </c>
       <c r="T75">
-        <v>0.15964999999999999</v>
+        <v>0.15966</v>
       </c>
       <c r="U75">
         <v>90.625</v>
@@ -10631,7 +10631,7 @@
         <v>89.0625</v>
       </c>
       <c r="T76">
-        <v>0.15687999999999999</v>
+        <v>0.15690000000000001</v>
       </c>
       <c r="U76">
         <v>89.0625</v>
@@ -10685,7 +10685,7 @@
         <v>89.0625</v>
       </c>
       <c r="AL76">
-        <v>0.15548999999999999</v>
+        <v>0.15551000000000001</v>
       </c>
       <c r="AM76">
         <v>89.0625</v>
@@ -10771,7 +10771,7 @@
         <v>87.5</v>
       </c>
       <c r="T77" s="1">
-        <v>0.15409</v>
+        <v>0.15411</v>
       </c>
       <c r="U77">
         <v>87.5</v>
@@ -10825,7 +10825,7 @@
         <v>87.5</v>
       </c>
       <c r="AL77">
-        <v>0.15273</v>
+        <v>0.15273999999999999</v>
       </c>
       <c r="AM77">
         <v>87.5</v>
@@ -10965,7 +10965,7 @@
         <v>85.9375</v>
       </c>
       <c r="AL78">
-        <v>0.15</v>
+        <v>0.151</v>
       </c>
       <c r="AM78">
         <v>85.9375</v>
@@ -11051,7 +11051,7 @@
         <v>84.375</v>
       </c>
       <c r="T79" s="1">
-        <v>0.14857000000000001</v>
+        <v>0.14860999999999999</v>
       </c>
       <c r="U79">
         <v>84.375</v>
@@ -11105,7 +11105,7 @@
         <v>84.375</v>
       </c>
       <c r="AL79">
-        <v>0.14724999999999999</v>
+        <v>0.14726</v>
       </c>
       <c r="AM79">
         <v>84.375</v>
@@ -11385,7 +11385,7 @@
         <v>81.25</v>
       </c>
       <c r="AL81">
-        <v>0.14177000000000001</v>
+        <v>0.14183000000000001</v>
       </c>
       <c r="AM81">
         <v>81.25</v>
@@ -11665,7 +11665,7 @@
         <v>78.125</v>
       </c>
       <c r="AL83">
-        <v>0.1363</v>
+        <v>0.13628000000000001</v>
       </c>
       <c r="AM83">
         <v>78.125</v>
@@ -11891,7 +11891,7 @@
         <v>75</v>
       </c>
       <c r="T85" s="1">
-        <v>0.13202</v>
+        <v>0.13205</v>
       </c>
       <c r="U85">
         <v>75</v>
@@ -12031,7 +12031,7 @@
         <v>73.4375</v>
       </c>
       <c r="T86" s="1">
-        <v>0.12927</v>
+        <v>0.12931999999999999</v>
       </c>
       <c r="U86">
         <v>73.4375</v>
@@ -12171,7 +12171,7 @@
         <v>71.875</v>
       </c>
       <c r="T87" s="1">
-        <v>0.1265</v>
+        <v>0.12648000000000001</v>
       </c>
       <c r="U87">
         <v>71.875</v>
@@ -12275,7 +12275,7 @@
         <v>70.3125</v>
       </c>
       <c r="H88" s="1">
-        <v>0.12373000000000001</v>
+        <v>0.12377000000000001</v>
       </c>
       <c r="I88">
         <v>70.3125</v>
@@ -12311,7 +12311,7 @@
         <v>70.3125</v>
       </c>
       <c r="T88" s="1">
-        <v>0.12375</v>
+        <v>0.12381</v>
       </c>
       <c r="U88">
         <v>70.3125</v>
@@ -12415,7 +12415,7 @@
         <v>68.75</v>
       </c>
       <c r="H89" s="1">
-        <v>0.12096</v>
+        <v>0.12099</v>
       </c>
       <c r="I89">
         <v>68.75</v>
@@ -12451,7 +12451,7 @@
         <v>68.75</v>
       </c>
       <c r="T89" s="1">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="U89">
         <v>68.75</v>
@@ -12695,7 +12695,7 @@
         <v>65.625</v>
       </c>
       <c r="H91" s="1">
-        <v>0.11545</v>
+        <v>0.11545999999999999</v>
       </c>
       <c r="I91">
         <v>65.625</v>
@@ -12731,7 +12731,7 @@
         <v>65.625</v>
       </c>
       <c r="T91">
-        <v>0.11547</v>
+        <v>0.11541</v>
       </c>
       <c r="U91">
         <v>65.625</v>
@@ -12871,7 +12871,7 @@
         <v>64.0625</v>
       </c>
       <c r="T92">
-        <v>0.11272</v>
+        <v>0.11277</v>
       </c>
       <c r="U92">
         <v>64.0625</v>
@@ -12975,7 +12975,7 @@
         <v>62.5</v>
       </c>
       <c r="H93">
-        <v>0.10993</v>
+        <v>0.10995000000000001</v>
       </c>
       <c r="I93">
         <v>62.5</v>
@@ -14617,7 +14617,7 @@
         <v>45.3125</v>
       </c>
       <c r="AP104">
-        <v>7.9460000000000003E-2</v>
+        <v>7.9450000000000007E-2</v>
       </c>
       <c r="AQ104">
         <v>45.3125</v>
@@ -14757,7 +14757,7 @@
         <v>43.75</v>
       </c>
       <c r="AP105">
-        <v>7.6730000000000007E-2</v>
+        <v>7.6780000000000001E-2</v>
       </c>
       <c r="AQ105">
         <v>43.75</v>
@@ -14897,7 +14897,7 @@
         <v>42.1875</v>
       </c>
       <c r="AP106">
-        <v>7.399E-2</v>
+        <v>7.3950000000000002E-2</v>
       </c>
       <c r="AQ106">
         <v>42.1875</v>
@@ -15037,7 +15037,7 @@
         <v>40.625</v>
       </c>
       <c r="AP107">
-        <v>7.1230000000000002E-2</v>
+        <v>7.1249999999999994E-2</v>
       </c>
       <c r="AQ107">
         <v>40.625</v>
@@ -15317,7 +15317,7 @@
         <v>37.5</v>
       </c>
       <c r="AP109">
-        <v>6.5740000000000007E-2</v>
+        <v>6.5710000000000005E-2</v>
       </c>
       <c r="AQ109">
         <v>37.5</v>
@@ -15457,7 +15457,7 @@
         <v>35.9375</v>
       </c>
       <c r="AP110">
-        <v>6.3009999999999997E-2</v>
+        <v>6.3020000000000007E-2</v>
       </c>
       <c r="AQ110">
         <v>35.9375</v>
@@ -15877,7 +15877,7 @@
         <v>31.25</v>
       </c>
       <c r="AP113">
-        <v>5.4800000000000001E-2</v>
+        <v>5.5100000000000003E-2</v>
       </c>
       <c r="AQ113">
         <v>31.25</v>
@@ -20789,7 +20789,7 @@
         <v>-23.4375</v>
       </c>
       <c r="AT148">
-        <v>-4.0980000000000003E-2</v>
+        <v>-4.095E-2</v>
       </c>
     </row>
     <row r="149" spans="1:46" x14ac:dyDescent="0.25">
@@ -20929,7 +20929,7 @@
         <v>-25</v>
       </c>
       <c r="AT149">
-        <v>-4.3740000000000001E-2</v>
+        <v>-4.3770000000000003E-2</v>
       </c>
     </row>
     <row r="150" spans="1:46" x14ac:dyDescent="0.25">
@@ -21209,7 +21209,7 @@
         <v>-28.125</v>
       </c>
       <c r="AT151">
-        <v>-4.9230000000000003E-2</v>
+        <v>-4.9250000000000002E-2</v>
       </c>
     </row>
     <row r="152" spans="1:46" x14ac:dyDescent="0.25">
@@ -21349,7 +21349,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AT152">
-        <v>-5.1979999999999998E-2</v>
+        <v>-5.1990000000000001E-2</v>
       </c>
     </row>
     <row r="153" spans="1:46" x14ac:dyDescent="0.25">
@@ -21489,7 +21489,7 @@
         <v>-31.25</v>
       </c>
       <c r="AT153">
-        <v>-5.4719999999999998E-2</v>
+        <v>-5.4769999999999999E-2</v>
       </c>
     </row>
     <row r="154" spans="1:46" x14ac:dyDescent="0.25">
@@ -21629,7 +21629,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AT154">
-        <v>-5.7430000000000002E-2</v>
+        <v>-5.7480000000000003E-2</v>
       </c>
     </row>
     <row r="155" spans="1:46" x14ac:dyDescent="0.25">
@@ -21769,7 +21769,7 @@
         <v>-34.375</v>
       </c>
       <c r="AT155">
-        <v>-5.9900000000000002E-2</v>
+        <v>-5.9909999999999998E-2</v>
       </c>
     </row>
     <row r="156" spans="1:46" x14ac:dyDescent="0.25">
@@ -21885,7 +21885,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AL156" s="1">
-        <v>-6.3009999999999997E-2</v>
+        <v>-6.3109999999999999E-2</v>
       </c>
       <c r="AM156">
         <v>-35.9375</v>
@@ -21909,7 +21909,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AT156">
-        <v>-6.275E-2</v>
+        <v>-6.2780000000000002E-2</v>
       </c>
     </row>
     <row r="157" spans="1:46" x14ac:dyDescent="0.25">
@@ -22025,7 +22025,7 @@
         <v>-37.5</v>
       </c>
       <c r="AL157" s="1">
-        <v>-6.5740000000000007E-2</v>
+        <v>-6.5780000000000005E-2</v>
       </c>
       <c r="AM157">
         <v>-37.5</v>
@@ -22049,7 +22049,7 @@
         <v>-37.5</v>
       </c>
       <c r="AT157">
-        <v>-6.547E-2</v>
+        <v>-6.5490000000000007E-2</v>
       </c>
     </row>
     <row r="158" spans="1:46" x14ac:dyDescent="0.25">
@@ -22165,7 +22165,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AL158" s="1">
-        <v>-6.8500000000000005E-2</v>
+        <v>-6.8479999999999999E-2</v>
       </c>
       <c r="AM158">
         <v>-39.0625</v>
@@ -22189,7 +22189,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AT158">
-        <v>-6.8229999999999999E-2</v>
+        <v>-6.8250000000000005E-2</v>
       </c>
     </row>
     <row r="159" spans="1:46" x14ac:dyDescent="0.25">
@@ -22305,7 +22305,7 @@
         <v>-40.625</v>
       </c>
       <c r="AL159" s="1">
-        <v>-7.1230000000000002E-2</v>
+        <v>-7.1249999999999994E-2</v>
       </c>
       <c r="AM159">
         <v>-40.625</v>
@@ -22329,7 +22329,7 @@
         <v>-40.625</v>
       </c>
       <c r="AT159">
-        <v>-7.0949999999999999E-2</v>
+        <v>-7.0940000000000003E-2</v>
       </c>
     </row>
     <row r="160" spans="1:46" x14ac:dyDescent="0.25">
@@ -22445,7 +22445,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AL160" s="1">
-        <v>-7.399E-2</v>
+        <v>-7.3959999999999998E-2</v>
       </c>
       <c r="AM160">
         <v>-42.1875</v>
@@ -22469,7 +22469,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AT160">
-        <v>-7.3690000000000005E-2</v>
+        <v>-7.3730000000000004E-2</v>
       </c>
     </row>
     <row r="161" spans="1:46" x14ac:dyDescent="0.25">
@@ -22585,7 +22585,7 @@
         <v>-43.75</v>
       </c>
       <c r="AL161" s="1">
-        <v>-7.6730000000000007E-2</v>
+        <v>-7.6780000000000001E-2</v>
       </c>
       <c r="AM161">
         <v>-43.75</v>
@@ -22609,7 +22609,7 @@
         <v>-43.75</v>
       </c>
       <c r="AT161">
-        <v>-7.6429999999999998E-2</v>
+        <v>-7.6450000000000004E-2</v>
       </c>
     </row>
     <row r="162" spans="1:46" x14ac:dyDescent="0.25">
@@ -22725,7 +22725,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AL162" s="1">
-        <v>-7.9460000000000003E-2</v>
+        <v>-7.9509999999999997E-2</v>
       </c>
       <c r="AM162">
         <v>-45.3125</v>
@@ -22749,7 +22749,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AT162">
-        <v>-7.9140000000000002E-2</v>
+        <v>-7.9159999999999994E-2</v>
       </c>
     </row>
     <row r="163" spans="1:46" x14ac:dyDescent="0.25">
@@ -22865,7 +22865,7 @@
         <v>-46.875</v>
       </c>
       <c r="AL163" s="1">
-        <v>-8.2189999999999999E-2</v>
+        <v>-8.2150000000000001E-2</v>
       </c>
       <c r="AM163">
         <v>-46.875</v>
@@ -22993,7 +22993,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AH164" s="1">
-        <v>-8.4870000000000001E-2</v>
+        <v>-7.6929999999999998E-2</v>
       </c>
       <c r="AI164">
         <v>-48.4375</v>
@@ -23005,7 +23005,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AL164" s="1">
-        <v>-8.4949999999999998E-2</v>
+        <v>-8.4959999999999994E-2</v>
       </c>
       <c r="AM164">
         <v>-48.4375</v>
@@ -23133,7 +23133,7 @@
         <v>-50</v>
       </c>
       <c r="AH165">
-        <v>-8.7599999999999997E-2</v>
+        <v>-8.7499999999999994E-2</v>
       </c>
       <c r="AI165">
         <v>-50</v>
@@ -23273,7 +23273,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AH166">
-        <v>-9.042E-2</v>
+        <v>-9.0399999999999994E-2</v>
       </c>
       <c r="AI166">
         <v>-51.5625</v>
@@ -23285,7 +23285,7 @@
         <v>-51.5625</v>
       </c>
       <c r="AL166" s="1">
-        <v>-9.0509999999999993E-2</v>
+        <v>-9.0550000000000005E-2</v>
       </c>
       <c r="AM166">
         <v>-51.5625</v>
@@ -23413,7 +23413,7 @@
         <v>-53.125</v>
       </c>
       <c r="AH167" s="1">
-        <v>-9.3160000000000007E-2</v>
+        <v>-9.3210000000000001E-2</v>
       </c>
       <c r="AI167">
         <v>-53.125</v>
@@ -23425,7 +23425,7 @@
         <v>-53.125</v>
       </c>
       <c r="AL167" s="1">
-        <v>-9.3240000000000003E-2</v>
+        <v>-9.325E-2</v>
       </c>
       <c r="AM167">
         <v>-53.125</v>
@@ -23693,7 +23693,7 @@
         <v>-56.25</v>
       </c>
       <c r="AH169">
-        <v>-9.8650000000000002E-2</v>
+        <v>-9.8710000000000006E-2</v>
       </c>
       <c r="AI169">
         <v>-56.25</v>
@@ -23833,7 +23833,7 @@
         <v>-57.8125</v>
       </c>
       <c r="AH170">
-        <v>-0.10138</v>
+        <v>-0.10141</v>
       </c>
       <c r="AI170">
         <v>-57.8125</v>
@@ -23973,7 +23973,7 @@
         <v>-59.375</v>
       </c>
       <c r="AH171">
-        <v>-0.10414</v>
+        <v>-0.10415000000000001</v>
       </c>
       <c r="AI171">
         <v>-59.375</v>
@@ -24113,7 +24113,7 @@
         <v>-60.9375</v>
       </c>
       <c r="AH172">
-        <v>-0.10687000000000001</v>
+        <v>-0.10689</v>
       </c>
       <c r="AI172">
         <v>-60.9375</v>
@@ -32117,7 +32117,7 @@
         <v>-50</v>
       </c>
       <c r="AP229">
-        <v>-8.7660000000000002E-2</v>
+        <v>-8.7650000000000006E-2</v>
       </c>
       <c r="AQ229">
         <v>-50</v>
@@ -32257,7 +32257,7 @@
         <v>-48.4375</v>
       </c>
       <c r="AP230">
-        <v>-8.4820000000000007E-2</v>
+        <v>-8.4779999999999994E-2</v>
       </c>
       <c r="AQ230">
         <v>-48.4375</v>
@@ -32397,7 +32397,7 @@
         <v>-46.875</v>
       </c>
       <c r="AP231">
-        <v>-8.2110000000000002E-2</v>
+        <v>-8.2119999999999999E-2</v>
       </c>
       <c r="AQ231">
         <v>-46.875</v>
@@ -32537,7 +32537,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AP232">
-        <v>-7.9350000000000004E-2</v>
+        <v>-7.9409999999999994E-2</v>
       </c>
       <c r="AQ232">
         <v>-45.3125</v>
@@ -32677,7 +32677,7 @@
         <v>-43.75</v>
       </c>
       <c r="AP233">
-        <v>-7.6619999999999994E-2</v>
+        <v>-7.6649999999999996E-2</v>
       </c>
       <c r="AQ233">
         <v>-43.75</v>
@@ -32817,7 +32817,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AP234">
-        <v>-7.3880000000000001E-2</v>
+        <v>-7.3870000000000005E-2</v>
       </c>
       <c r="AQ234">
         <v>-42.1875</v>
@@ -33097,7 +33097,7 @@
         <v>-39.0625</v>
       </c>
       <c r="AP236">
-        <v>-6.8409999999999999E-2</v>
+        <v>-6.8449999999999997E-2</v>
       </c>
       <c r="AQ236">
         <v>-39.0625</v>
@@ -33237,7 +33237,7 @@
         <v>-37.5</v>
       </c>
       <c r="AP237">
-        <v>-6.5659999999999996E-2</v>
+        <v>-6.565E-2</v>
       </c>
       <c r="AQ237">
         <v>-37.5</v>
@@ -33377,7 +33377,7 @@
         <v>-35.9375</v>
       </c>
       <c r="AP238">
-        <v>-6.2899999999999998E-2</v>
+        <v>-6.3100000000000003E-2</v>
       </c>
       <c r="AQ238">
         <v>-35.9375</v>
@@ -33517,7 +33517,7 @@
         <v>-34.375</v>
       </c>
       <c r="AP239">
-        <v>-6.0170000000000001E-2</v>
+        <v>-6.021E-2</v>
       </c>
       <c r="AQ239">
         <v>-34.375</v>
@@ -33657,7 +33657,7 @@
         <v>-32.8125</v>
       </c>
       <c r="AP240">
-        <v>-5.7430000000000002E-2</v>
+        <v>-5.7450000000000001E-2</v>
       </c>
       <c r="AQ240">
         <v>-32.8125</v>
@@ -33797,7 +33797,7 @@
         <v>-31.25</v>
       </c>
       <c r="AP241">
-        <v>-5.4699999999999999E-2</v>
+        <v>-5.4710000000000002E-2</v>
       </c>
       <c r="AQ241">
         <v>-31.25</v>
@@ -33937,7 +33937,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AP242">
-        <v>-5.1959999999999999E-2</v>
+        <v>-5.1970000000000002E-2</v>
       </c>
       <c r="AQ242">
         <v>-29.6875</v>
@@ -34077,7 +34077,7 @@
         <v>-28.125</v>
       </c>
       <c r="AP243">
-        <v>-4.9250000000000002E-2</v>
+        <v>-4.931E-2</v>
       </c>
       <c r="AQ243">
         <v>-28.125</v>
